--- a/AAVE/COPA/copa_AAVE.xlsx
+++ b/AAVE/COPA/copa_AAVE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonLi\Algoverse\PJEA\AAVE\COPA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D478BD-8520-468D-A5C6-F97381478BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332F4AC4-972C-4B04-AC51-DA2C6C7CECF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="26055" windowHeight="14024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1951" yWindow="1951" windowWidth="19380" windowHeight="10040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -636,7 +636,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1012,8 +1012,8 @@
         <v>My body cast a shadow ova the grass. 'cause. choice 1 The sun be risin'. or choice 2 The grass was cut.</v>
       </c>
       <c r="K2" t="str">
-        <f>CONCATENATE(A2," ",D2,". choice1: ", B2, " or choice 2: ", C2)</f>
-        <v>My body cast a shadow over the grass. cause. choice1: The sun was rising. or choice 2: The grass was cut.</v>
+        <f>CONCATENATE(A2," ",D2,". Choice 1: ", B2, " or choice 2: ", C2)</f>
+        <v>My body cast a shadow over the grass. cause. Choice 1: The sun was rising. or choice 2: The grass was cut.</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1049,8 +1049,8 @@
         <v>The woman put up with her friend's difficult behavior. 'cause. choice 1 The woman knew her friend was going through it. or choice 2 The woman felt like her friend took advantage of her kindness.</v>
       </c>
       <c r="K3" t="str">
-        <f t="shared" ref="K3:K31" si="1">CONCATENATE(A3," ",D3,". choice1: ", B3, " or choice 2: ", C3)</f>
-        <v>The woman tolerated her friend's difficult behavior. cause. choice1: The woman knew her friend was going through a hard time. or choice 2: The woman felt that her friend took advantage of her kindness.</v>
+        <f t="shared" ref="K3:K31" si="1">CONCATENATE(A3," ",D3,". Choice 1: ", B3, " or choice 2: ", C3)</f>
+        <v>The woman tolerated her friend's difficult behavior. cause. Choice 1: The woman knew her friend was going through a hard time. or choice 2: The woman felt that her friend took advantage of her kindness.</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K4" t="str">
         <f t="shared" si="1"/>
-        <v>The women met for coffee. cause. choice1: The cafe reopened in a new location. or choice 2: They wanted to catch up with each other.</v>
+        <v>The women met for coffee. cause. Choice 1: The cafe reopened in a new location. or choice 2: They wanted to catch up with each other.</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="K5" t="str">
         <f t="shared" si="1"/>
-        <v>The runner wore shorts. cause. choice1: The forecast predicted high temperatures. or choice 2: She planned to run along the beach.</v>
+        <v>The runner wore shorts. cause. Choice 1: The forecast predicted high temperatures. or choice 2: She planned to run along the beach.</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="K6" t="str">
         <f t="shared" si="1"/>
-        <v>The guests of the party hid behind the couch. cause. choice1: It was a surprise party. or choice 2: It was a birthday party.</v>
+        <v>The guests of the party hid behind the couch. cause. Choice 1: It was a surprise party. or choice 2: It was a birthday party.</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K7" t="str">
         <f t="shared" si="1"/>
-        <v>The politician lost the election. cause. choice1: He ran negative campaign ads. or choice 2: No one voted for him.</v>
+        <v>The politician lost the election. cause. Choice 1: He ran negative campaign ads. or choice 2: No one voted for him.</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K8" t="str">
         <f t="shared" si="1"/>
-        <v>The stain came out of the shirt. cause. choice1: I patched the shirt. or choice 2: I bleached the shirt.</v>
+        <v>The stain came out of the shirt. cause. Choice 1: I patched the shirt. or choice 2: I bleached the shirt.</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
-        <v>The man got a discount on his groceries. cause. choice1: He greeted the cashier. or choice 2: He used a coupon.</v>
+        <v>The man got a discount on his groceries. cause. Choice 1: He greeted the cashier. or choice 2: He used a coupon.</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
-        <v>The physician misdiagnosed the patient. effect. choice1: The patient filed a malpractice lawsuit against the physician. or choice 2: The patient disclosed confidential information to the physician.</v>
+        <v>The physician misdiagnosed the patient. effect. Choice 1: The patient filed a malpractice lawsuit against the physician. or choice 2: The patient disclosed confidential information to the physician.</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
-        <v>The customer filed a complaint with the store manager. cause. choice1: The sales associate undercharged the customer. or choice 2: The sales associate acted rude to the customer.</v>
+        <v>The customer filed a complaint with the store manager. cause. Choice 1: The sales associate undercharged the customer. or choice 2: The sales associate acted rude to the customer.</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
-        <v>The woman repaired her faucet. cause. choice1: The faucet was leaky. or choice 2: The faucet was turned off.</v>
+        <v>The woman repaired her faucet. cause. Choice 1: The faucet was leaky. or choice 2: The faucet was turned off.</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
-        <v>The elderly woman suffered a stroke. effect. choice1: The woman's daughter came over to clean her house. or choice 2: The woman's daughter moved in to take care of her.</v>
+        <v>The elderly woman suffered a stroke. effect. Choice 1: The woman's daughter came over to clean her house. or choice 2: The woman's daughter moved in to take care of her.</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
-        <v>The pond froze over for the winter. effect. choice1: People skated on the pond. or choice 2: People brought boats to the pond.</v>
+        <v>The pond froze over for the winter. effect. Choice 1: People skated on the pond. or choice 2: People brought boats to the pond.</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
-        <v>The offender violated parole. effect. choice1: She was sent back to jail. or choice 2: She stole money from a church.</v>
+        <v>The offender violated parole. effect. Choice 1: She was sent back to jail. or choice 2: She stole money from a church.</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
-        <v>I poured water on my sleeping friend. effect. choice1: My friend awoke. or choice 2: My friend snored.</v>
+        <v>I poured water on my sleeping friend. effect. Choice 1: My friend awoke. or choice 2: My friend snored.</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
-        <v>The girl gasped. cause. choice1: Her friend stuck an ice cube down her back. or choice 2: Her friend gave her a pat on the back.</v>
+        <v>The girl gasped. cause. Choice 1: Her friend stuck an ice cube down her back. or choice 2: Her friend gave her a pat on the back.</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
-        <v>The shirt shrunk. cause. choice1: I poured bleach on it. or choice 2: I put it in the dryer.</v>
+        <v>The shirt shrunk. cause. Choice 1: I poured bleach on it. or choice 2: I put it in the dryer.</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="K19" t="str">
         <f t="shared" si="1"/>
-        <v>It got dark outside. effect. choice1: Snowflakes began to fall from the sky. or choice 2: The moon became visible in the sky.</v>
+        <v>It got dark outside. effect. Choice 1: Snowflakes began to fall from the sky. or choice 2: The moon became visible in the sky.</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K20" t="str">
         <f t="shared" si="1"/>
-        <v>I hung up the phone. cause. choice1: The caller said goodbye to me. or choice 2: The caller identified himself to me.</v>
+        <v>I hung up the phone. cause. Choice 1: The caller said goodbye to me. or choice 2: The caller identified himself to me.</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="K21" t="str">
         <f t="shared" si="1"/>
-        <v>The woman's ring slipped off in the shower. effect. choice1: The woman polished the ring. or choice 2: The ring went down the drain.</v>
+        <v>The woman's ring slipped off in the shower. effect. Choice 1: The woman polished the ring. or choice 2: The ring went down the drain.</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="K22" t="str">
         <f t="shared" si="1"/>
-        <v>The girl received a trophy. cause. choice1: She won a spelling bee. or choice 2: She made a new friend.</v>
+        <v>The girl received a trophy. cause. Choice 1: She won a spelling bee. or choice 2: She made a new friend.</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="K23" t="str">
         <f t="shared" si="1"/>
-        <v>The woman's date wanted to look like a gentleman. effect. choice1: He opened the door for her. or choice 2: He asked her if she liked sushi.</v>
+        <v>The woman's date wanted to look like a gentleman. effect. Choice 1: He opened the door for her. or choice 2: He asked her if she liked sushi.</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="K24" t="str">
         <f t="shared" si="1"/>
-        <v>The farmland needed irrigation. effect. choice1: A canal was constructed. or choice 2: A flood occurred.</v>
+        <v>The farmland needed irrigation. effect. Choice 1: A canal was constructed. or choice 2: A flood occurred.</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K25" t="str">
         <f t="shared" si="1"/>
-        <v>The host cancelled the party. cause. choice1: She was certain she had the flu. or choice 2: She worried she would catch the flu.</v>
+        <v>The host cancelled the party. cause. Choice 1: She was certain she had the flu. or choice 2: She worried she would catch the flu.</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K26" t="str">
         <f t="shared" si="1"/>
-        <v>The woman gave the man her phone number. cause. choice1: She was attracted to him. or choice 2: She was repulsed by him.</v>
+        <v>The woman gave the man her phone number. cause. Choice 1: She was attracted to him. or choice 2: She was repulsed by him.</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="K27" t="str">
         <f t="shared" si="1"/>
-        <v>The skydiver glided safely to the ground. cause. choice1: She opened her parachute. or choice 2: She jumped out of the plane.</v>
+        <v>The skydiver glided safely to the ground. cause. Choice 1: She opened her parachute. or choice 2: She jumped out of the plane.</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="K28" t="str">
         <f t="shared" si="1"/>
-        <v>The toddler became cranky. effect. choice1: Her mother put her down for a nap. or choice 2: Her mother fixed her hair into pigtails.</v>
+        <v>The toddler became cranky. effect. Choice 1: Her mother put her down for a nap. or choice 2: Her mother fixed her hair into pigtails.</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="K29" t="str">
         <f t="shared" si="1"/>
-        <v>The child became immune to the disease. cause. choice1: He avoided exposure to the disease. or choice 2: He received the vaccine for the disease.</v>
+        <v>The child became immune to the disease. cause. Choice 1: He avoided exposure to the disease. or choice 2: He received the vaccine for the disease.</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="K30" t="str">
         <f t="shared" si="1"/>
-        <v>The grape juice fermented. effect. choice1: The juice turned to wine. or choice 2: The juice evaporated.</v>
+        <v>The grape juice fermented. effect. Choice 1: The juice turned to wine. or choice 2: The juice evaporated.</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="K31" t="str">
         <f t="shared" si="1"/>
-        <v>The friends' debate dragged on interminably. cause. choice1: The friends saw eye to eye. or choice 2: The friends were splitting hairs.</v>
+        <v>The friends' debate dragged on interminably. cause. Choice 1: The friends saw eye to eye. or choice 2: The friends were splitting hairs.</v>
       </c>
     </row>
   </sheetData>
